--- a/GOA CEATTLE/Model runs/GOA_25/Results/GOA 2025 Pollock ESP Indices.xlsx
+++ b/GOA CEATTLE/Model runs/GOA_25/Results/GOA 2025 Pollock ESP Indices.xlsx
@@ -379,7 +379,7 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>1.097581040023245</v>
+        <v>1.097588456198057</v>
       </c>
       <c r="C2">
         <v>1.39</v>
@@ -390,7 +390,7 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>1.043597164227701</v>
+        <v>1.043602585237845</v>
       </c>
       <c r="C3">
         <v>1.39</v>
@@ -401,7 +401,7 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>1.037162025215967</v>
+        <v>1.037165378278189</v>
       </c>
       <c r="C4">
         <v>1.39</v>
@@ -412,7 +412,7 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>1.047377770214407</v>
+        <v>1.04738072927743</v>
       </c>
       <c r="C5">
         <v>1.39</v>
@@ -423,7 +423,7 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>1.181967240262691</v>
+        <v>1.18197024029842</v>
       </c>
       <c r="C6">
         <v>1.39</v>
@@ -434,7 +434,7 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>1.088751952306997</v>
+        <v>1.088754223225</v>
       </c>
       <c r="C7">
         <v>1.39</v>
@@ -445,7 +445,7 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>1.170096489448562</v>
+        <v>1.170100526936732</v>
       </c>
       <c r="C8">
         <v>1.39</v>
@@ -456,7 +456,7 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>1.104413499546979</v>
+        <v>1.104417925017955</v>
       </c>
       <c r="C9">
         <v>1.39</v>
@@ -467,7 +467,7 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>1.058272202292097</v>
+        <v>1.058276256283762</v>
       </c>
       <c r="C10">
         <v>1.39</v>
@@ -478,7 +478,7 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>1.062447701512605</v>
+        <v>1.062452453750212</v>
       </c>
       <c r="C11">
         <v>1.39</v>
@@ -489,7 +489,7 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>1.177919181101003</v>
+        <v>1.17792511224713</v>
       </c>
       <c r="C12">
         <v>1.39</v>
@@ -500,7 +500,7 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>1.183888917481075</v>
+        <v>1.183895029436661</v>
       </c>
       <c r="C13">
         <v>1.39</v>
@@ -511,7 +511,7 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>1.173318151569904</v>
+        <v>1.173324512904437</v>
       </c>
       <c r="C14">
         <v>1.39</v>
@@ -522,7 +522,7 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>1.213372512003002</v>
+        <v>1.213380359742142</v>
       </c>
       <c r="C15">
         <v>1.39</v>
@@ -533,7 +533,7 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>1.341792277987117</v>
+        <v>1.341802641932386</v>
       </c>
       <c r="C16">
         <v>1.39</v>
@@ -544,7 +544,7 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>1.523558697672517</v>
+        <v>1.523572468362719</v>
       </c>
       <c r="C17">
         <v>1.39</v>
@@ -555,7 +555,7 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>1.536127411367094</v>
+        <v>1.536142932146508</v>
       </c>
       <c r="C18">
         <v>1.39</v>
@@ -566,7 +566,7 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>1.524554839360333</v>
+        <v>1.524571545588274</v>
       </c>
       <c r="C19">
         <v>1.39</v>
@@ -577,7 +577,7 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>1.390385715012588</v>
+        <v>1.390400663006129</v>
       </c>
       <c r="C20">
         <v>1.39</v>
@@ -588,7 +588,7 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>1.403101789315251</v>
+        <v>1.403117725692209</v>
       </c>
       <c r="C21">
         <v>1.39</v>
@@ -599,7 +599,7 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>1.356907991947279</v>
+        <v>1.356923346781115</v>
       </c>
       <c r="C22">
         <v>1.39</v>
@@ -610,7 +610,7 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>1.427556542331817</v>
+        <v>1.427572604677509</v>
       </c>
       <c r="C23">
         <v>1.39</v>
@@ -621,7 +621,7 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>1.268696440548173</v>
+        <v>1.268709391879775</v>
       </c>
       <c r="C24">
         <v>1.39</v>
@@ -632,7 +632,7 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>1.292537814994758</v>
+        <v>1.292550410260347</v>
       </c>
       <c r="C25">
         <v>1.39</v>
@@ -643,7 +643,7 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>1.414253398072342</v>
+        <v>1.414267237733652</v>
       </c>
       <c r="C26">
         <v>1.39</v>
@@ -654,7 +654,7 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>1.453689463397295</v>
+        <v>1.453703812565279</v>
       </c>
       <c r="C27">
         <v>1.39</v>
@@ -665,7 +665,7 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>1.722480722149767</v>
+        <v>1.722498463991725</v>
       </c>
       <c r="C28">
         <v>1.39</v>
@@ -676,7 +676,7 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>1.705134752231215</v>
+        <v>1.705152147372128</v>
       </c>
       <c r="C29">
         <v>1.39</v>
@@ -687,7 +687,7 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>1.707184376150274</v>
+        <v>1.707201799749769</v>
       </c>
       <c r="C30">
         <v>1.39</v>
@@ -698,7 +698,7 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>1.583272749741553</v>
+        <v>1.583288355508122</v>
       </c>
       <c r="C31">
         <v>1.39</v>
@@ -709,7 +709,7 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>1.439776923751885</v>
+        <v>1.439790843290796</v>
       </c>
       <c r="C32">
         <v>1.39</v>
@@ -720,7 +720,7 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>1.388393534255255</v>
+        <v>1.388406311536215</v>
       </c>
       <c r="C33">
         <v>1.39</v>
@@ -731,7 +731,7 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>1.270929018181143</v>
+        <v>1.270939937981732</v>
       </c>
       <c r="C34">
         <v>1.39</v>
@@ -742,7 +742,7 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>1.364669014398655</v>
+        <v>1.364680718636035</v>
       </c>
       <c r="C35">
         <v>1.39</v>
@@ -753,7 +753,7 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>1.233861279113114</v>
+        <v>1.233870781917433</v>
       </c>
       <c r="C36">
         <v>1.39</v>
@@ -764,7 +764,7 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>1.108104114035232</v>
+        <v>1.108112030825793</v>
       </c>
       <c r="C37">
         <v>1.39</v>
@@ -775,7 +775,7 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>1.066319167917038</v>
+        <v>1.066325100252663</v>
       </c>
       <c r="C38">
         <v>1.39</v>
@@ -786,7 +786,7 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>0.9447894167967084</v>
+        <v>0.9447951178154051</v>
       </c>
       <c r="C39">
         <v>1.39</v>
@@ -797,7 +797,7 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>1.194217569751554</v>
+        <v>1.194224267323106</v>
       </c>
       <c r="C40">
         <v>1.39</v>
@@ -808,7 +808,7 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>1.245989652913284</v>
+        <v>1.245996804749773</v>
       </c>
       <c r="C41">
         <v>1.39</v>
@@ -819,7 +819,7 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>1.148097532457734</v>
+        <v>1.14810497119427</v>
       </c>
       <c r="C42">
         <v>1.39</v>
@@ -830,7 +830,7 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>1.140973505272833</v>
+        <v>1.140981460300467</v>
       </c>
       <c r="C43">
         <v>1.39</v>
@@ -841,7 +841,7 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>1.210501316849586</v>
+        <v>1.21051084531026</v>
       </c>
       <c r="C44">
         <v>1.39</v>
@@ -852,7 +852,7 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>1.112549414045697</v>
+        <v>1.112558040561237</v>
       </c>
       <c r="C45">
         <v>1.39</v>
@@ -863,7 +863,7 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>1.136020839085067</v>
+        <v>1.136029477097558</v>
       </c>
       <c r="C46">
         <v>1.39</v>
@@ -874,7 +874,7 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>1.224176820848452</v>
+        <v>1.224187673966418</v>
       </c>
       <c r="C47">
         <v>1.39</v>
@@ -885,7 +885,7 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>1.201396901936497</v>
+        <v>1.201407276633915</v>
       </c>
       <c r="C48">
         <v>1.39</v>
@@ -896,7 +896,7 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>1.232997633692018</v>
+        <v>1.233008874355831</v>
       </c>
       <c r="C49">
         <v>1.39</v>
@@ -907,7 +907,7 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>1.22366124154077</v>
+        <v>1.223672701358401</v>
       </c>
       <c r="C50">
         <v>1.39</v>
@@ -955,16 +955,16 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>2007859.707364169</v>
+        <v>2007845.242895141</v>
       </c>
       <c r="C2">
-        <v>175553.6566672345</v>
+        <v>175552.4789046343</v>
       </c>
       <c r="D2">
-        <v>3036119.364756608</v>
+        <v>3035998.758195594</v>
       </c>
       <c r="E2">
-        <v>317915.3731165807</v>
+        <v>317901.0430100303</v>
       </c>
     </row>
     <row r="3">
@@ -972,16 +972,16 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>2633749.134768014</v>
+        <v>2633727.991839611</v>
       </c>
       <c r="C3">
-        <v>168196.7219640591</v>
+        <v>168195.3800873102</v>
       </c>
       <c r="D3">
-        <v>3948793.971595712</v>
+        <v>3948628.621034544</v>
       </c>
       <c r="E3">
-        <v>323968.5484767408</v>
+        <v>323952.9385300164</v>
       </c>
     </row>
     <row r="4">
@@ -989,16 +989,16 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>3940459.069326187</v>
+        <v>3940426.051273123</v>
       </c>
       <c r="C4">
-        <v>181377.5699492705</v>
+        <v>181375.8754561994</v>
       </c>
       <c r="D4">
-        <v>5712805.110274306</v>
+        <v>5712564.944646887</v>
       </c>
       <c r="E4">
-        <v>359962.4344856557</v>
+        <v>359944.772316128</v>
       </c>
     </row>
     <row r="5">
@@ -1006,16 +1006,16 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>4396417.273326533</v>
+        <v>4396379.750901855</v>
       </c>
       <c r="C5">
-        <v>250934.8087815898</v>
+        <v>250932.3110860498</v>
       </c>
       <c r="D5">
-        <v>6964646.217840071</v>
+        <v>6964350.14672369</v>
       </c>
       <c r="E5">
-        <v>501290.6865754549</v>
+        <v>501266.6502584897</v>
       </c>
     </row>
     <row r="6">
@@ -1023,16 +1023,16 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>4752169.19123671</v>
+        <v>4752127.85180536</v>
       </c>
       <c r="C6">
-        <v>277772.6812375736</v>
+        <v>277769.8568456457</v>
       </c>
       <c r="D6">
-        <v>8127519.407997037</v>
+        <v>8127175.367859315</v>
       </c>
       <c r="E6">
-        <v>554016.1550581505</v>
+        <v>553990.4062026171</v>
       </c>
     </row>
     <row r="7">
@@ -1040,16 +1040,16 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>4618926.262161462</v>
+        <v>4618885.558258761</v>
       </c>
       <c r="C7">
-        <v>450135.8449747546</v>
+        <v>450131.3112412578</v>
       </c>
       <c r="D7">
-        <v>8133579.721082004</v>
+        <v>8133239.159525326</v>
       </c>
       <c r="E7">
-        <v>887801.9426703047</v>
+        <v>887762.6549874599</v>
       </c>
     </row>
     <row r="8">
@@ -1057,16 +1057,16 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>4260131.280030172</v>
+        <v>4260092.976771728</v>
       </c>
       <c r="C8">
-        <v>631421.9290622056</v>
+        <v>631415.5071628207</v>
       </c>
       <c r="D8">
-        <v>7687984.641475307</v>
+        <v>7687669.57414314</v>
       </c>
       <c r="E8">
-        <v>1240023.409051954</v>
+        <v>1239970.384653626</v>
       </c>
     </row>
     <row r="9">
@@ -1074,16 +1074,16 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>3933145.165971277</v>
+        <v>3933108.763531457</v>
       </c>
       <c r="C9">
-        <v>714030.1077251922</v>
+        <v>714022.3781466705</v>
       </c>
       <c r="D9">
-        <v>7057589.975771941</v>
+        <v>7057303.141152964</v>
       </c>
       <c r="E9">
-        <v>1418260.087382192</v>
+        <v>1418199.70717808</v>
       </c>
     </row>
     <row r="10">
@@ -1091,16 +1091,16 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>3868043.365255778</v>
+        <v>3868006.846544441</v>
       </c>
       <c r="C10">
-        <v>675742.5965432212</v>
+        <v>675734.4875321677</v>
       </c>
       <c r="D10">
-        <v>6722034.849427611</v>
+        <v>6721764.824851676</v>
       </c>
       <c r="E10">
-        <v>1373328.847005244</v>
+        <v>1373269.3480529</v>
       </c>
     </row>
     <row r="11">
@@ -1108,16 +1108,16 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>3352324.165434996</v>
+        <v>3352291.032657342</v>
       </c>
       <c r="C11">
-        <v>638204.7473906034</v>
+        <v>638196.4686547145</v>
       </c>
       <c r="D11">
-        <v>6125543.914374941</v>
+        <v>6125295.629452349</v>
       </c>
       <c r="E11">
-        <v>1321621.694925416</v>
+        <v>1321563.976985453</v>
       </c>
     </row>
     <row r="12">
@@ -1125,16 +1125,16 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>3059739.430641994</v>
+        <v>3059709.395060429</v>
       </c>
       <c r="C12">
-        <v>607025.6142229487</v>
+        <v>607017.8308207151</v>
       </c>
       <c r="D12">
-        <v>5724480.762547648</v>
+        <v>5724252.912354455</v>
       </c>
       <c r="E12">
-        <v>1214302.654824289</v>
+        <v>1214251.479870412</v>
       </c>
     </row>
     <row r="13">
@@ -1142,16 +1142,16 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>2947233.425198101</v>
+        <v>2947205.471536255</v>
       </c>
       <c r="C13">
-        <v>604565.5794397906</v>
+        <v>604558.073261812</v>
       </c>
       <c r="D13">
-        <v>5361252.882692979</v>
+        <v>5361047.49007086</v>
       </c>
       <c r="E13">
-        <v>1161498.051894695</v>
+        <v>1161451.184250085</v>
       </c>
     </row>
     <row r="14">
@@ -1159,16 +1159,16 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>3101951.111546562</v>
+        <v>3101924.114438871</v>
       </c>
       <c r="C14">
-        <v>611116.85140338</v>
+        <v>611109.9278409031</v>
       </c>
       <c r="D14">
-        <v>5276276.490846737</v>
+        <v>5276086.102888305</v>
       </c>
       <c r="E14">
-        <v>1130909.016228726</v>
+        <v>1130865.814030638</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>3148107.223835214</v>
+        <v>3148081.012229795</v>
       </c>
       <c r="C15">
-        <v>621624.0943961077</v>
+        <v>621617.2893283615</v>
       </c>
       <c r="D15">
-        <v>5269374.435259496</v>
+        <v>5269192.711253908</v>
       </c>
       <c r="E15">
-        <v>1120030.245918865</v>
+        <v>1119989.099063435</v>
       </c>
     </row>
     <row r="16">
@@ -1193,16 +1193,16 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>2960589.517961777</v>
+        <v>2960565.781068275</v>
       </c>
       <c r="C16">
-        <v>611024.566045191</v>
+        <v>611017.939574784</v>
       </c>
       <c r="D16">
-        <v>5093640.248383371</v>
+        <v>5093466.182145818</v>
       </c>
       <c r="E16">
-        <v>1073414.393737557</v>
+        <v>1073376.073668437</v>
       </c>
     </row>
     <row r="17">
@@ -1210,16 +1210,16 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>2676945.837491598</v>
+        <v>2676924.744511935</v>
       </c>
       <c r="C17">
-        <v>548372.1536987959</v>
+        <v>548366.4853202614</v>
       </c>
       <c r="D17">
-        <v>4711506.617018387</v>
+        <v>4711349.627146987</v>
       </c>
       <c r="E17">
-        <v>953420.7119255686</v>
+        <v>953387.4035745296</v>
       </c>
     </row>
     <row r="18">
@@ -1227,16 +1227,16 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>2382293.614413986</v>
+        <v>2382275.079424646</v>
       </c>
       <c r="C18">
-        <v>571983.4380982991</v>
+        <v>571977.945633658</v>
       </c>
       <c r="D18">
-        <v>4191954.277075848</v>
+        <v>4191817.26045708</v>
       </c>
       <c r="E18">
-        <v>988013.980361814</v>
+        <v>987980.2596018547</v>
       </c>
     </row>
     <row r="19">
@@ -1244,16 +1244,16 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>1971116.089459329</v>
+        <v>1971100.491545745</v>
       </c>
       <c r="C19">
-        <v>644290.6115991718</v>
+        <v>644284.7691245348</v>
       </c>
       <c r="D19">
-        <v>3436435.206478821</v>
+        <v>3436325.033557948</v>
       </c>
       <c r="E19">
-        <v>1108421.545699305</v>
+        <v>1108384.497388091</v>
       </c>
     </row>
     <row r="20">
@@ -1261,16 +1261,16 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>1819437.244887279</v>
+        <v>1819423.128205526</v>
       </c>
       <c r="C20">
-        <v>520863.1436083287</v>
+        <v>520858.4286069481</v>
       </c>
       <c r="D20">
-        <v>3103611.223992504</v>
+        <v>3103521.514746078</v>
       </c>
       <c r="E20">
-        <v>881221.0883596925</v>
+        <v>881192.2401597816</v>
       </c>
     </row>
     <row r="21">
@@ -1278,16 +1278,16 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>1508544.273262149</v>
+        <v>1508532.480408451</v>
       </c>
       <c r="C21">
-        <v>465653.9943973837</v>
+        <v>465649.8328263983</v>
       </c>
       <c r="D21">
-        <v>2525587.543784331</v>
+        <v>2525513.603155257</v>
       </c>
       <c r="E21">
-        <v>768912.2090204152</v>
+        <v>768887.7652658421</v>
       </c>
     </row>
     <row r="22">
@@ -1295,16 +1295,16 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>1369834.713254353</v>
+        <v>1369824.385486577</v>
       </c>
       <c r="C22">
-        <v>404375.6364238732</v>
+        <v>404371.9984340814</v>
       </c>
       <c r="D22">
-        <v>2225873.252379279</v>
+        <v>2225807.20213801</v>
       </c>
       <c r="E22">
-        <v>650023.4538947635</v>
+        <v>650003.24022779</v>
       </c>
     </row>
     <row r="23">
@@ -1312,16 +1312,16 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>1257443.716640534</v>
+        <v>1257434.153855453</v>
       </c>
       <c r="C23">
-        <v>311715.9222033464</v>
+        <v>311712.9536121772</v>
       </c>
       <c r="D23">
-        <v>2031206.863779543</v>
+        <v>2031145.156750803</v>
       </c>
       <c r="E23">
-        <v>497325.2965783414</v>
+        <v>497309.5890080909</v>
       </c>
     </row>
     <row r="24">
@@ -1329,16 +1329,16 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>1011213.402721316</v>
+        <v>1011205.17498703</v>
       </c>
       <c r="C24">
-        <v>286906.5054875324</v>
+        <v>286903.6384188071</v>
       </c>
       <c r="D24">
-        <v>1624518.74664307</v>
+        <v>1624467.079142717</v>
       </c>
       <c r="E24">
-        <v>463590.0459328524</v>
+        <v>463574.8023292369</v>
       </c>
     </row>
     <row r="25">
@@ -1346,16 +1346,16 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>1127972.491209249</v>
+        <v>1127963.400758995</v>
       </c>
       <c r="C25">
-        <v>269751.1426256065</v>
+        <v>269748.3637777008</v>
       </c>
       <c r="D25">
-        <v>1784648.249502205</v>
+        <v>1784593.603857828</v>
       </c>
       <c r="E25">
-        <v>441856.5845424868</v>
+        <v>441841.5971651183</v>
       </c>
     </row>
     <row r="26">
@@ -1363,16 +1363,16 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>1289906.670317224</v>
+        <v>1289896.415423989</v>
       </c>
       <c r="C26">
-        <v>253574.9371944148</v>
+        <v>253572.2008965711</v>
       </c>
       <c r="D26">
-        <v>2081987.575781263</v>
+        <v>2081924.541612861</v>
       </c>
       <c r="E26">
-        <v>417193.8026814249</v>
+        <v>417179.3555880819</v>
       </c>
     </row>
     <row r="27">
@@ -1380,16 +1380,16 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>1355139.830250575</v>
+        <v>1355129.362864228</v>
       </c>
       <c r="C27">
-        <v>218224.9030712057</v>
+        <v>218222.4811873815</v>
       </c>
       <c r="D27">
-        <v>2200500.498185677</v>
+        <v>2200426.991267793</v>
       </c>
       <c r="E27">
-        <v>359832.9529023452</v>
+        <v>359820.2987067073</v>
       </c>
     </row>
     <row r="28">
@@ -1397,16 +1397,16 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>1391564.480075061</v>
+        <v>1391553.917169667</v>
       </c>
       <c r="C28">
-        <v>209434.7103421459</v>
+        <v>209432.4955930643</v>
       </c>
       <c r="D28">
-        <v>2362187.3575992</v>
+        <v>2362109.322532767</v>
       </c>
       <c r="E28">
-        <v>347071.5445841457</v>
+        <v>347059.3167761965</v>
       </c>
     </row>
     <row r="29">
@@ -1414,16 +1414,16 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>1191149.46285248</v>
+        <v>1191140.268966905</v>
       </c>
       <c r="C29">
-        <v>240491.7640687801</v>
+        <v>240489.5585583791</v>
       </c>
       <c r="D29">
-        <v>2052757.849187086</v>
+        <v>2052689.507634928</v>
       </c>
       <c r="E29">
-        <v>402493.293522216</v>
+        <v>402479.2900108373</v>
       </c>
     </row>
     <row r="30">
@@ -1431,16 +1431,16 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>1062234.068730647</v>
+        <v>1062225.720394563</v>
       </c>
       <c r="C30">
-        <v>297429.0279610472</v>
+        <v>297426.307245929</v>
       </c>
       <c r="D30">
-        <v>1874435.330318904</v>
+        <v>1874375.705839005</v>
       </c>
       <c r="E30">
-        <v>498056.906197912</v>
+        <v>498039.7198405658</v>
       </c>
     </row>
     <row r="31">
@@ -1448,16 +1448,16 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>1150760.390385721</v>
+        <v>1150751.148143911</v>
       </c>
       <c r="C31">
-        <v>330935.5531077248</v>
+        <v>330932.4600114336</v>
       </c>
       <c r="D31">
-        <v>2057160.385242943</v>
+        <v>2057099.26109698</v>
       </c>
       <c r="E31">
-        <v>559080.0286331096</v>
+        <v>559060.5112489692</v>
       </c>
     </row>
     <row r="32">
@@ -1465,16 +1465,16 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>1272809.338198474</v>
+        <v>1272799.064532946</v>
       </c>
       <c r="C32">
-        <v>304496.9840007312</v>
+        <v>304494.0099764777</v>
       </c>
       <c r="D32">
-        <v>2162613.683509645</v>
+        <v>2162546.589682247</v>
       </c>
       <c r="E32">
-        <v>508479.2717997045</v>
+        <v>508461.4339099066</v>
       </c>
     </row>
     <row r="33">
@@ -1482,16 +1482,16 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>1665133.088453164</v>
+        <v>1665120.666916394</v>
       </c>
       <c r="C33">
-        <v>312890.6999804648</v>
+        <v>312887.6336955865</v>
       </c>
       <c r="D33">
-        <v>2700811.984254137</v>
+        <v>2700725.754267067</v>
       </c>
       <c r="E33">
-        <v>511193.143218854</v>
+        <v>511175.37399387</v>
       </c>
     </row>
     <row r="34">
@@ -1499,16 +1499,16 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>2127278.902022468</v>
+        <v>2127264.012115007</v>
       </c>
       <c r="C34">
-        <v>314537.6422159414</v>
+        <v>314534.6723136795</v>
       </c>
       <c r="D34">
-        <v>3365689.786263912</v>
+        <v>3365577.569938309</v>
       </c>
       <c r="E34">
-        <v>501289.9965989101</v>
+        <v>501272.8222174208</v>
       </c>
     </row>
     <row r="35">
@@ -1516,16 +1516,16 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>2111412.224821743</v>
+        <v>2111397.713195134</v>
       </c>
       <c r="C35">
-        <v>424064.1461082129</v>
+        <v>424060.5247950304</v>
       </c>
       <c r="D35">
-        <v>3335252.767608684</v>
+        <v>3335140.270757179</v>
       </c>
       <c r="E35">
-        <v>671949.9031523232</v>
+        <v>671927.0884498185</v>
       </c>
     </row>
     <row r="36">
@@ -1533,16 +1533,16 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>2106156.160989753</v>
+        <v>2106141.907612046</v>
       </c>
       <c r="C36">
-        <v>485524.8570296922</v>
+        <v>485520.9946334239</v>
       </c>
       <c r="D36">
-        <v>3275167.580586616</v>
+        <v>3275058.8898282</v>
       </c>
       <c r="E36">
-        <v>772027.1319281959</v>
+        <v>772001.0316701664</v>
       </c>
     </row>
     <row r="37">
@@ -1550,16 +1550,16 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>2087670.614156351</v>
+        <v>2087656.649350725</v>
       </c>
       <c r="C37">
-        <v>511296.875235245</v>
+        <v>511292.9463580013</v>
       </c>
       <c r="D37">
-        <v>3246402.713883803</v>
+        <v>3246293.757988465</v>
       </c>
       <c r="E37">
-        <v>812329.5631466459</v>
+        <v>812302.0764937559</v>
       </c>
     </row>
     <row r="38">
@@ -1567,16 +1567,16 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>3018101.688074827</v>
+        <v>3018082.78638503</v>
       </c>
       <c r="C38">
-        <v>557744.4801948655</v>
+        <v>557740.1601458053</v>
       </c>
       <c r="D38">
-        <v>3903912.704122051</v>
+        <v>3903787.844199528</v>
       </c>
       <c r="E38">
-        <v>879227.5545196161</v>
+        <v>879197.6613986334</v>
       </c>
     </row>
     <row r="39">
@@ -1584,16 +1584,16 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>4410167.111547083</v>
+        <v>4410141.104742318</v>
       </c>
       <c r="C39">
-        <v>438327.0816693206</v>
+        <v>438323.6301207932</v>
       </c>
       <c r="D39">
-        <v>5922329.427819761</v>
+        <v>5922134.757692982</v>
       </c>
       <c r="E39">
-        <v>684893.6030294471</v>
+        <v>684870.1160556627</v>
       </c>
     </row>
     <row r="40">
@@ -1601,16 +1601,16 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>3781477.510504014</v>
+        <v>3781454.912546854</v>
       </c>
       <c r="C40">
-        <v>420931.2757771069</v>
+        <v>420927.8490202263</v>
       </c>
       <c r="D40">
-        <v>5616945.53099269</v>
+        <v>5616752.661185066</v>
       </c>
       <c r="E40">
-        <v>661360.3868087988</v>
+        <v>661337.0666063643</v>
       </c>
     </row>
     <row r="41">
@@ -1618,16 +1618,16 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>3430849.593050319</v>
+        <v>3430828.731764157</v>
       </c>
       <c r="C41">
-        <v>448332.1806115034</v>
+        <v>448328.896348957</v>
       </c>
       <c r="D41">
-        <v>5421978.552571273</v>
+        <v>5421793.375482589</v>
       </c>
       <c r="E41">
-        <v>713226.9087701413</v>
+        <v>713202.0132133355</v>
       </c>
     </row>
     <row r="42">
@@ -1635,16 +1635,16 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>2490815.466005283</v>
+        <v>2490799.383666268</v>
       </c>
       <c r="C42">
-        <v>613712.8448993239</v>
+        <v>613708.4574122744</v>
       </c>
       <c r="D42">
-        <v>3998188.410253572</v>
+        <v>3998052.999812827</v>
       </c>
       <c r="E42">
-        <v>990030.2121990842</v>
+        <v>989996.2226312272</v>
       </c>
     </row>
     <row r="43">
@@ -1652,16 +1652,16 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>2290222.864215963</v>
+        <v>2290208.012504171</v>
       </c>
       <c r="C43">
-        <v>610385.5624798405</v>
+        <v>610380.9893202846</v>
       </c>
       <c r="D43">
-        <v>3522587.668385425</v>
+        <v>3522472.907053827</v>
       </c>
       <c r="E43">
-        <v>998504.1454593929</v>
+        <v>998469.8651368673</v>
       </c>
     </row>
     <row r="44">
@@ -1669,16 +1669,16 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>2156446.547640687</v>
+        <v>2156431.761689671</v>
       </c>
       <c r="C44">
-        <v>505136.6245305802</v>
+        <v>505132.5923564186</v>
       </c>
       <c r="D44">
-        <v>3244294.530887544</v>
+        <v>3244191.001352493</v>
       </c>
       <c r="E44">
-        <v>826984.332908803</v>
+        <v>826955.76546854</v>
       </c>
     </row>
     <row r="45">
@@ -1686,16 +1686,16 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>1933530.004106254</v>
+        <v>1933516.811087859</v>
       </c>
       <c r="C45">
-        <v>385125.603022043</v>
+        <v>385122.2940255876</v>
       </c>
       <c r="D45">
-        <v>2928800.551866228</v>
+        <v>2928703.536607862</v>
       </c>
       <c r="E45">
-        <v>627731.0913633691</v>
+        <v>627709.2616921717</v>
       </c>
     </row>
     <row r="46">
@@ -1703,16 +1703,16 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>2301289.253788692</v>
+        <v>2301273.954646214</v>
       </c>
       <c r="C46">
-        <v>412448.4347459176</v>
+        <v>412444.8570698298</v>
       </c>
       <c r="D46">
-        <v>3462364.582433661</v>
+        <v>3462252.010470998</v>
       </c>
       <c r="E46">
-        <v>661635.335052929</v>
+        <v>661612.4395295742</v>
       </c>
     </row>
     <row r="47">
@@ -1720,16 +1720,16 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>2122780.278163188</v>
+        <v>2122766.293062239</v>
       </c>
       <c r="C47">
-        <v>407161.7782872809</v>
+        <v>407158.2879914262</v>
       </c>
       <c r="D47">
-        <v>3371296.782894497</v>
+        <v>3371184.275593183</v>
       </c>
       <c r="E47">
-        <v>649712.4401803586</v>
+        <v>649690.141245365</v>
       </c>
     </row>
     <row r="48">
@@ -1737,16 +1737,16 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>1850648.29287862</v>
+        <v>1850635.49781005</v>
       </c>
       <c r="C48">
-        <v>435996.3765139236</v>
+        <v>435992.6220992496</v>
       </c>
       <c r="D48">
-        <v>3034006.360728368</v>
+        <v>3033901.468778184</v>
       </c>
       <c r="E48">
-        <v>708166.8861830872</v>
+        <v>708142.3733444787</v>
       </c>
     </row>
     <row r="49">
@@ -1754,16 +1754,16 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>1646709.579358229</v>
+        <v>1646698.127904122</v>
       </c>
       <c r="C49">
-        <v>429766.080531378</v>
+        <v>429762.341935744</v>
       </c>
       <c r="D49">
-        <v>2784334.388993299</v>
+        <v>2784235.173256356</v>
       </c>
       <c r="E49">
-        <v>720259.8979277691</v>
+        <v>720234.452307819</v>
       </c>
     </row>
     <row r="50">
@@ -1771,16 +1771,16 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>1504479.809384214</v>
+        <v>1504469.447085539</v>
       </c>
       <c r="C50">
-        <v>415909.3492265092</v>
+        <v>415905.7003800459</v>
       </c>
       <c r="D50">
-        <v>2479414.873520942</v>
+        <v>2479322.611261403</v>
       </c>
       <c r="E50">
-        <v>720097.3381007027</v>
+        <v>720071.3808975153</v>
       </c>
     </row>
   </sheetData>
@@ -1810,7 +1810,7 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>565817.7478727907</v>
+        <v>565808.3437864749</v>
       </c>
     </row>
     <row r="3">
@@ -1818,7 +1818,7 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>672846.9785241846</v>
+        <v>672834.7065894996</v>
       </c>
     </row>
     <row r="4">
@@ -1826,7 +1826,7 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>981497.4814859792</v>
+        <v>981475.8915260585</v>
       </c>
     </row>
     <row r="5">
@@ -1834,7 +1834,7 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>804556.9937161752</v>
+        <v>804541.537650367</v>
       </c>
     </row>
     <row r="6">
@@ -1842,7 +1842,7 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>656412.5786310259</v>
+        <v>656400.2604832116</v>
       </c>
     </row>
     <row r="7">
@@ -1850,7 +1850,7 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>463121.309037832</v>
+        <v>463112.094482751</v>
       </c>
     </row>
     <row r="8">
@@ -1858,7 +1858,7 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>468617.5891535148</v>
+        <v>468609.0265636053</v>
       </c>
     </row>
     <row r="9">
@@ -1866,7 +1866,7 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>464236.2263667394</v>
+        <v>464227.4937972752</v>
       </c>
     </row>
     <row r="10">
@@ -1874,7 +1874,7 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>601191.7209335845</v>
+        <v>601180.1297192568</v>
       </c>
     </row>
     <row r="11">
@@ -1882,7 +1882,7 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>463880.0338663428</v>
+        <v>463873.7477250121</v>
       </c>
     </row>
     <row r="12">
@@ -1890,7 +1890,7 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>321611.9755198311</v>
+        <v>321608.0375919272</v>
       </c>
     </row>
     <row r="13">
@@ -1898,7 +1898,7 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>320213.391779802</v>
+        <v>320208.6041310969</v>
       </c>
     </row>
     <row r="14">
@@ -1906,7 +1906,7 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>493803.5372040871</v>
+        <v>493795.9546564154</v>
       </c>
     </row>
     <row r="15">
@@ -1914,7 +1914,7 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>582344.4743898951</v>
+        <v>582337.6236889205</v>
       </c>
     </row>
     <row r="16">
@@ -1922,7 +1922,7 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>421345.6615866553</v>
+        <v>421342.1922548235</v>
       </c>
     </row>
     <row r="17">
@@ -1930,7 +1930,7 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>358754.6978096991</v>
+        <v>358752.8034420264</v>
       </c>
     </row>
     <row r="18">
@@ -1938,7 +1938,7 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>276620.8322962104</v>
+        <v>276619.8409220167</v>
       </c>
     </row>
     <row r="19">
@@ -1946,7 +1946,7 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>209854.8064417307</v>
+        <v>209854.4399241378</v>
       </c>
     </row>
     <row r="20">
@@ -1954,7 +1954,7 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>362164.4990921089</v>
+        <v>362165.3896218904</v>
       </c>
     </row>
     <row r="21">
@@ -1962,7 +1962,7 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>258935.4365524415</v>
+        <v>258936.0620098945</v>
       </c>
     </row>
     <row r="22">
@@ -1970,7 +1970,7 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>205920.1063554714</v>
+        <v>205920.502978744</v>
       </c>
     </row>
     <row r="23">
@@ -1978,7 +1978,7 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>168528.3325366297</v>
+        <v>168528.4582069018</v>
       </c>
     </row>
     <row r="24">
@@ -1986,7 +1986,7 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>126884.0932181379</v>
+        <v>126883.7434867801</v>
       </c>
     </row>
     <row r="25">
@@ -1994,7 +1994,7 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>274443.0588332785</v>
+        <v>274441.782631506</v>
       </c>
     </row>
     <row r="26">
@@ -2002,7 +2002,7 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>395495.422864331</v>
+        <v>395493.909905154</v>
       </c>
     </row>
     <row r="27">
@@ -2010,7 +2010,7 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>237735.9152894968</v>
+        <v>237735.3011597943</v>
       </c>
     </row>
     <row r="28">
@@ -2018,7 +2018,7 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>249666.5833521323</v>
+        <v>249666.1393856967</v>
       </c>
     </row>
     <row r="29">
@@ -2026,7 +2026,7 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>157504.0601317582</v>
+        <v>157503.963768131</v>
       </c>
     </row>
     <row r="30">
@@ -2034,7 +2034,7 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>209515.9834672767</v>
+        <v>209515.9392932192</v>
       </c>
     </row>
     <row r="31">
@@ -2042,7 +2042,7 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>397884.6502944106</v>
+        <v>397883.9241127404</v>
       </c>
     </row>
     <row r="32">
@@ -2050,7 +2050,7 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>400733.6605507842</v>
+        <v>400732.6398456627</v>
       </c>
     </row>
     <row r="33">
@@ -2058,7 +2058,7 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>465013.9142936616</v>
+        <v>465011.9323850896</v>
       </c>
     </row>
     <row r="34">
@@ -2066,7 +2066,7 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>420472.7198186734</v>
+        <v>420470.8632191192</v>
       </c>
     </row>
     <row r="35">
@@ -2074,7 +2074,7 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>275897.0230030258</v>
+        <v>275895.9447982733</v>
       </c>
     </row>
     <row r="36">
@@ -2082,7 +2082,7 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>276875.1993648682</v>
+        <v>276873.530501748</v>
       </c>
     </row>
     <row r="37">
@@ -2090,7 +2090,7 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>219956.0237780943</v>
+        <v>219955.226306591</v>
       </c>
     </row>
     <row r="38">
@@ -2098,7 +2098,7 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>618173.4867267546</v>
+        <v>618165.3955467022</v>
       </c>
     </row>
     <row r="39">
@@ -2106,7 +2106,7 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>722725.2382877105</v>
+        <v>722721.2111155097</v>
       </c>
     </row>
     <row r="40">
@@ -2114,7 +2114,7 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>329971.9286994873</v>
+        <v>329970.1285124361</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>148037.4578061212</v>
+        <v>148036.7358404725</v>
       </c>
     </row>
     <row r="42">
@@ -2130,7 +2130,7 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>102719.1597435149</v>
+        <v>102718.2813950759</v>
       </c>
     </row>
     <row r="43">
@@ -2138,7 +2138,7 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>261035.9056402774</v>
+        <v>261033.8115212174</v>
       </c>
     </row>
     <row r="44">
@@ -2146,7 +2146,7 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>394621.9066026972</v>
+        <v>394619.2037358399</v>
       </c>
     </row>
     <row r="45">
@@ -2154,7 +2154,7 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>230290.1262561969</v>
+        <v>230289.1749124965</v>
       </c>
     </row>
     <row r="46">
@@ -2162,7 +2162,7 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>376904.271290549</v>
+        <v>376901.210193265</v>
       </c>
     </row>
     <row r="47">
@@ -2170,7 +2170,7 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>317331.6504851082</v>
+        <v>317330.1302623357</v>
       </c>
     </row>
     <row r="48">
@@ -2178,7 +2178,7 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>173575.4851167296</v>
+        <v>173574.1914551917</v>
       </c>
     </row>
     <row r="49">
@@ -2186,7 +2186,7 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>201291.8074152197</v>
+        <v>201289.4344942649</v>
       </c>
     </row>
     <row r="50">
@@ -2194,7 +2194,7 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>214546.8586074036</v>
+        <v>214543.6900729825</v>
       </c>
     </row>
   </sheetData>
@@ -2229,10 +2229,10 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>831457.5734833662</v>
+        <v>818901.7438421543</v>
       </c>
       <c r="C2">
-        <v>1213756.402705</v>
+        <v>3127090.790178705</v>
       </c>
     </row>
     <row r="3">
@@ -2240,10 +2240,10 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>733238.5585369874</v>
+        <v>692469.5923369258</v>
       </c>
       <c r="C3">
-        <v>1539231.099644411</v>
+        <v>4115167.563669467</v>
       </c>
     </row>
     <row r="4">
@@ -2251,10 +2251,10 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>1038803.891426633</v>
+        <v>1119171.52418877</v>
       </c>
       <c r="C4">
-        <v>2164196.114019342</v>
+        <v>6313406.095968594</v>
       </c>
     </row>
     <row r="5">
@@ -2262,10 +2262,10 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>1534673.7680431</v>
+        <v>1719710.361526844</v>
       </c>
       <c r="C5">
-        <v>2941904.60393328</v>
+        <v>6920176.702611217</v>
       </c>
     </row>
     <row r="6">
@@ -2273,10 +2273,10 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>2260079.203425329</v>
+        <v>2523342.227527448</v>
       </c>
       <c r="C6">
-        <v>4099979.142966515</v>
+        <v>7348706.073728448</v>
       </c>
     </row>
     <row r="7">
@@ -2284,10 +2284,10 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>3100749.179185321</v>
+        <v>3523275.58687141</v>
       </c>
       <c r="C7">
-        <v>3923245.358224797</v>
+        <v>6033892.201803592</v>
       </c>
     </row>
     <row r="8">
@@ -2295,10 +2295,10 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>3643068.718271548</v>
+        <v>3807595.365578287</v>
       </c>
       <c r="C8">
-        <v>4248242.900884521</v>
+        <v>5965329.76453747</v>
       </c>
     </row>
     <row r="9">
@@ -2306,10 +2306,10 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>3122840.720374057</v>
+        <v>3125519.62077599</v>
       </c>
       <c r="C9">
-        <v>3815135.786652745</v>
+        <v>5236252.083315586</v>
       </c>
     </row>
     <row r="10">
@@ -2317,10 +2317,10 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>2917445.961830657</v>
+        <v>2703045.908708634</v>
       </c>
       <c r="C10">
-        <v>3491184.219380836</v>
+        <v>5444132.054492569</v>
       </c>
     </row>
     <row r="11">
@@ -2328,10 +2328,10 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>2596800.268496969</v>
+        <v>2420157.671398826</v>
       </c>
       <c r="C11">
-        <v>3251087.602924511</v>
+        <v>4866519.325737772</v>
       </c>
     </row>
     <row r="12">
@@ -2339,10 +2339,10 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>2640145.534910261</v>
+        <v>2343761.727040155</v>
       </c>
       <c r="C12">
-        <v>3390608.473374646</v>
+        <v>4347043.97707231</v>
       </c>
     </row>
     <row r="13">
@@ -2350,10 +2350,10 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>2945790.667944508</v>
+        <v>2779488.021823645</v>
       </c>
       <c r="C13">
-        <v>3172513.57197574</v>
+        <v>3831289.855242538</v>
       </c>
     </row>
     <row r="14">
@@ -2361,10 +2361,10 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>2608093.562082246</v>
+        <v>2288605.233025757</v>
       </c>
       <c r="C14">
-        <v>2838797.073946434</v>
+        <v>3955314.484059888</v>
       </c>
     </row>
     <row r="15">
@@ -2372,10 +2372,10 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>2325449.061673436</v>
+        <v>1844358.225399732</v>
       </c>
       <c r="C15">
-        <v>2749827.808944681</v>
+        <v>4064879.416593348</v>
       </c>
     </row>
     <row r="16">
@@ -2383,10 +2383,10 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>2209721.393819637</v>
+        <v>1733302.52894104</v>
       </c>
       <c r="C16">
-        <v>2828210.095399257</v>
+        <v>3679795.860359211</v>
       </c>
     </row>
     <row r="17">
@@ -2394,10 +2394,10 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>2440232.980115087</v>
+        <v>2133935.747796869</v>
       </c>
       <c r="C17">
-        <v>2827796.024872747</v>
+        <v>3318474.749323837</v>
       </c>
     </row>
     <row r="18">
@@ -2405,10 +2405,10 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>2402155.220098099</v>
+        <v>2065036.410727433</v>
       </c>
       <c r="C18">
-        <v>2594163.236537176</v>
+        <v>2670591.277151921</v>
       </c>
     </row>
     <row r="19">
@@ -2416,10 +2416,10 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>2114495.868779742</v>
+        <v>1674262.634586988</v>
       </c>
       <c r="C19">
-        <v>2218861.148639961</v>
+        <v>2114846.582141691</v>
       </c>
     </row>
     <row r="20">
@@ -2427,10 +2427,10 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>1676968.916912061</v>
+        <v>1274756.635587564</v>
       </c>
       <c r="C20">
-        <v>1792344.218672015</v>
+        <v>2203859.472115347</v>
       </c>
     </row>
     <row r="21">
@@ -2438,10 +2438,10 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>1432038.30304668</v>
+        <v>1039829.687945345</v>
       </c>
       <c r="C21">
-        <v>1540455.682946455</v>
+        <v>1858008.5005847</v>
       </c>
     </row>
     <row r="22">
@@ -2449,10 +2449,10 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>1075662.671026039</v>
+        <v>799774.8959190156</v>
       </c>
       <c r="C22">
-        <v>1301409.326651039</v>
+        <v>1592874.844645676</v>
       </c>
     </row>
     <row r="23">
@@ -2460,10 +2460,10 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>1203866.74345238</v>
+        <v>1009378.136155477</v>
       </c>
       <c r="C23">
-        <v>1323785.497308748</v>
+        <v>1508997.841062149</v>
       </c>
     </row>
     <row r="24">
@@ -2471,10 +2471,10 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>839238.9033736796</v>
+        <v>762954.6210647761</v>
       </c>
       <c r="C24">
-        <v>917160.996671021</v>
+        <v>1168351.372074684</v>
       </c>
     </row>
     <row r="25">
@@ -2482,10 +2482,10 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>810350.2347183207</v>
+        <v>648711.1399721873</v>
       </c>
       <c r="C25">
-        <v>927284.8110803731</v>
+        <v>1596554.621821222</v>
       </c>
     </row>
     <row r="26">
@@ -2493,10 +2493,10 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>842588.7922974837</v>
+        <v>603504.6997222889</v>
       </c>
       <c r="C26">
-        <v>1047158.822372804</v>
+        <v>2060207.728072652</v>
       </c>
     </row>
     <row r="27">
@@ -2504,10 +2504,10 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>678947.6608607277</v>
+        <v>526886.2697501911</v>
       </c>
       <c r="C27">
-        <v>1080248.730396991</v>
+        <v>1744642.587122003</v>
       </c>
     </row>
     <row r="28">
@@ -2515,10 +2515,10 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>899284.583936856</v>
+        <v>897209.5005985997</v>
       </c>
       <c r="C28">
-        <v>1303109.055925366</v>
+        <v>1834103.316129021</v>
       </c>
     </row>
     <row r="29">
@@ -2526,10 +2526,10 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>1105200.678575599</v>
+        <v>1106699.562181479</v>
       </c>
       <c r="C29">
-        <v>1176877.663194451</v>
+        <v>1405439.472980234</v>
       </c>
     </row>
     <row r="30">
@@ -2537,10 +2537,10 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>1031982.577565637</v>
+        <v>897690.4217553301</v>
       </c>
       <c r="C30">
-        <v>1108778.315131954</v>
+        <v>1390989.341114613</v>
       </c>
     </row>
     <row r="31">
@@ -2548,10 +2548,10 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>1017441.079718483</v>
+        <v>727987.612628901</v>
       </c>
       <c r="C31">
-        <v>1131098.237875957</v>
+        <v>1791354.121213139</v>
       </c>
     </row>
     <row r="32">
@@ -2559,10 +2559,10 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>968156.273967433</v>
+        <v>580299.254984961</v>
       </c>
       <c r="C32">
-        <v>1159337.589347229</v>
+        <v>1838227.812102924</v>
       </c>
     </row>
     <row r="33">
@@ -2570,10 +2570,10 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>1031938.20478419</v>
+        <v>607063.5267140283</v>
       </c>
       <c r="C33">
-        <v>1439619.81070494</v>
+        <v>2265404.603502725</v>
       </c>
     </row>
     <row r="34">
@@ -2581,10 +2581,10 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>1357378.727730347</v>
+        <v>912804.5434278145</v>
       </c>
       <c r="C34">
-        <v>1830226.692407667</v>
+        <v>2289961.8864225</v>
       </c>
     </row>
     <row r="35">
@@ -2592,10 +2592,10 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>1714897.374629569</v>
+        <v>1227615.744003769</v>
       </c>
       <c r="C35">
-        <v>2167375.833193181</v>
+        <v>2341665.367560621</v>
       </c>
     </row>
     <row r="36">
@@ -2603,10 +2603,10 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>1856423.471543937</v>
+        <v>1356365.27134778</v>
       </c>
       <c r="C36">
-        <v>2080881.627471013</v>
+        <v>2261715.055438231</v>
       </c>
     </row>
     <row r="37">
@@ -2614,10 +2614,10 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>1877721.861602931</v>
+        <v>1231401.864778639</v>
       </c>
       <c r="C37">
-        <v>2100102.431549272</v>
+        <v>1900319.74102412</v>
       </c>
     </row>
     <row r="38">
@@ -2625,10 +2625,10 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>1713388.228591635</v>
+        <v>1032183.954144622</v>
       </c>
       <c r="C38">
-        <v>2055165.194338841</v>
+        <v>4228326.482296822</v>
       </c>
     </row>
     <row r="39">
@@ -2636,10 +2636,10 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>1574998.07665178</v>
+        <v>1097605.613342867</v>
       </c>
       <c r="C39">
-        <v>2672870.831573954</v>
+        <v>5453410.631073124</v>
       </c>
     </row>
     <row r="40">
@@ -2647,10 +2647,10 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>1196134.284452483</v>
+        <v>847589.7677249339</v>
       </c>
       <c r="C40">
-        <v>2969161.074897319</v>
+        <v>4939315.956229024</v>
       </c>
     </row>
     <row r="41">
@@ -2658,10 +2658,10 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>3140365.910484307</v>
+        <v>3882443.287277925</v>
       </c>
       <c r="C41">
-        <v>3214389.153977143</v>
+        <v>4055224.918263834</v>
       </c>
     </row>
     <row r="42">
@@ -2669,10 +2669,10 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>2209731.570910481</v>
+        <v>2585274.507624729</v>
       </c>
       <c r="C42">
-        <v>2241095.33217091</v>
+        <v>2789701.559388924</v>
       </c>
     </row>
     <row r="43">
@@ -2680,10 +2680,10 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>1869751.713551802</v>
+        <v>1923496.553382277</v>
       </c>
       <c r="C43">
-        <v>1959259.922382646</v>
+        <v>2858836.407181586</v>
       </c>
     </row>
     <row r="44">
@@ -2691,10 +2691,10 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>1505736.891367293</v>
+        <v>1430605.629595596</v>
       </c>
       <c r="C44">
-        <v>1761207.708892158</v>
+        <v>3071852.705597342</v>
       </c>
     </row>
     <row r="45">
@@ -2702,10 +2702,10 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>1050517.916159463</v>
+        <v>984529.0974939265</v>
       </c>
       <c r="C45">
-        <v>1434890.512664969</v>
+        <v>2300517.232638885</v>
       </c>
     </row>
     <row r="46">
@@ -2713,10 +2713,10 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>1228079.2716317</v>
+        <v>1191683.384640264</v>
       </c>
       <c r="C46">
-        <v>1676157.917211765</v>
+        <v>2867447.37577673</v>
       </c>
     </row>
     <row r="47">
@@ -2724,10 +2724,10 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>1398780.803069673</v>
+        <v>1394047.569830063</v>
       </c>
       <c r="C47">
-        <v>1789605.340444966</v>
+        <v>2637714.949601834</v>
       </c>
     </row>
     <row r="48">
@@ -2735,10 +2735,10 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>1201364.028365662</v>
+        <v>1078224.688352826</v>
       </c>
       <c r="C48">
-        <v>1648651.650166569</v>
+        <v>2152741.595077149</v>
       </c>
     </row>
     <row r="49">
@@ -2746,10 +2746,10 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>1449603.415321556</v>
+        <v>1425391.509265588</v>
       </c>
       <c r="C49">
-        <v>1580930.177877493</v>
+        <v>2005656.068728045</v>
       </c>
     </row>
     <row r="50">
@@ -2757,10 +2757,10 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>1179505.744192149</v>
+        <v>1042048.510193462</v>
       </c>
       <c r="C50">
-        <v>1395329.032690369</v>
+        <v>1803534.525319292</v>
       </c>
     </row>
   </sheetData>

--- a/GOA CEATTLE/Model runs/GOA_25/Results/GOA 2025 Pollock ESP Indices.xlsx
+++ b/GOA CEATTLE/Model runs/GOA_25/Results/GOA 2025 Pollock ESP Indices.xlsx
@@ -379,7 +379,7 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>1.097588456198057</v>
+        <v>1.055985927235866</v>
       </c>
       <c r="C2">
         <v>1.39</v>
@@ -390,7 +390,7 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>1.043602585237845</v>
+        <v>1.011561217118384</v>
       </c>
       <c r="C3">
         <v>1.39</v>
@@ -401,7 +401,7 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>1.037165378278189</v>
+        <v>1.017485579969043</v>
       </c>
       <c r="C4">
         <v>1.39</v>
@@ -412,7 +412,7 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>1.04738072927743</v>
+        <v>1.026864708842818</v>
       </c>
       <c r="C5">
         <v>1.39</v>
@@ -423,7 +423,7 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>1.18197024029842</v>
+        <v>1.153546323692749</v>
       </c>
       <c r="C6">
         <v>1.39</v>
@@ -434,7 +434,7 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>1.088754223225</v>
+        <v>1.05615983026752</v>
       </c>
       <c r="C7">
         <v>1.39</v>
@@ -445,7 +445,7 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>1.170100526936732</v>
+        <v>1.116722969155024</v>
       </c>
       <c r="C8">
         <v>1.39</v>
@@ -456,7 +456,7 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>1.104417925017955</v>
+        <v>1.04298484996346</v>
       </c>
       <c r="C9">
         <v>1.39</v>
@@ -467,7 +467,7 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>1.058276256283762</v>
+        <v>1.001436094358261</v>
       </c>
       <c r="C10">
         <v>1.39</v>
@@ -478,7 +478,7 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>1.062452453750212</v>
+        <v>1.002886166397288</v>
       </c>
       <c r="C11">
         <v>1.39</v>
@@ -489,7 +489,7 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>1.17792511224713</v>
+        <v>1.111390019651691</v>
       </c>
       <c r="C12">
         <v>1.39</v>
@@ -500,7 +500,7 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>1.183895029436661</v>
+        <v>1.12740191815318</v>
       </c>
       <c r="C13">
         <v>1.39</v>
@@ -511,7 +511,7 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>1.173324512904437</v>
+        <v>1.126633045885698</v>
       </c>
       <c r="C14">
         <v>1.39</v>
@@ -522,7 +522,7 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>1.213380359742142</v>
+        <v>1.149563506383061</v>
       </c>
       <c r="C15">
         <v>1.39</v>
@@ -533,7 +533,7 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>1.341802641932386</v>
+        <v>1.240995505582846</v>
       </c>
       <c r="C16">
         <v>1.39</v>
@@ -544,7 +544,7 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>1.523572468362719</v>
+        <v>1.37248164619821</v>
       </c>
       <c r="C17">
         <v>1.39</v>
@@ -555,7 +555,7 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>1.536142932146508</v>
+        <v>1.350771409024008</v>
       </c>
       <c r="C18">
         <v>1.39</v>
@@ -566,7 +566,7 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>1.524571545588274</v>
+        <v>1.331181758877992</v>
       </c>
       <c r="C19">
         <v>1.39</v>
@@ -577,7 +577,7 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>1.390400663006129</v>
+        <v>1.246715202801957</v>
       </c>
       <c r="C20">
         <v>1.39</v>
@@ -588,7 +588,7 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>1.403117725692209</v>
+        <v>1.248735470133013</v>
       </c>
       <c r="C21">
         <v>1.39</v>
@@ -599,7 +599,7 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>1.356923346781115</v>
+        <v>1.205998025235679</v>
       </c>
       <c r="C22">
         <v>1.39</v>
@@ -610,7 +610,7 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>1.427572604677509</v>
+        <v>1.299841718232511</v>
       </c>
       <c r="C23">
         <v>1.39</v>
@@ -621,7 +621,7 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>1.268709391879775</v>
+        <v>1.174017578610937</v>
       </c>
       <c r="C24">
         <v>1.39</v>
@@ -632,7 +632,7 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>1.292550410260347</v>
+        <v>1.192848549242347</v>
       </c>
       <c r="C25">
         <v>1.39</v>
@@ -643,7 +643,7 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>1.414267237733652</v>
+        <v>1.31216064225147</v>
       </c>
       <c r="C26">
         <v>1.39</v>
@@ -654,7 +654,7 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>1.453703812565279</v>
+        <v>1.326439320367004</v>
       </c>
       <c r="C27">
         <v>1.39</v>
@@ -665,7 +665,7 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>1.722498463991725</v>
+        <v>1.541574903189974</v>
       </c>
       <c r="C28">
         <v>1.39</v>
@@ -676,7 +676,7 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>1.705152147372128</v>
+        <v>1.517572204732313</v>
       </c>
       <c r="C29">
         <v>1.39</v>
@@ -687,7 +687,7 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>1.707201799749769</v>
+        <v>1.511918155203907</v>
       </c>
       <c r="C30">
         <v>1.39</v>
@@ -698,7 +698,7 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>1.583288355508122</v>
+        <v>1.40551304382369</v>
       </c>
       <c r="C31">
         <v>1.39</v>
@@ -709,7 +709,7 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>1.439790843290796</v>
+        <v>1.295833470712185</v>
       </c>
       <c r="C32">
         <v>1.39</v>
@@ -720,7 +720,7 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>1.388406311536215</v>
+        <v>1.273377904568953</v>
       </c>
       <c r="C33">
         <v>1.39</v>
@@ -731,7 +731,7 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>1.270939937981732</v>
+        <v>1.174921707977844</v>
       </c>
       <c r="C34">
         <v>1.39</v>
@@ -742,7 +742,7 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>1.364680718636035</v>
+        <v>1.30873079516881</v>
       </c>
       <c r="C35">
         <v>1.39</v>
@@ -753,7 +753,7 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>1.233870781917433</v>
+        <v>1.176790527873781</v>
       </c>
       <c r="C36">
         <v>1.39</v>
@@ -764,7 +764,7 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>1.108112030825793</v>
+        <v>1.067388574469584</v>
       </c>
       <c r="C37">
         <v>1.39</v>
@@ -775,7 +775,7 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>1.066325100252663</v>
+        <v>1.048940638075451</v>
       </c>
       <c r="C38">
         <v>1.39</v>
@@ -786,7 +786,7 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>0.9447951178154051</v>
+        <v>0.9271806133599604</v>
       </c>
       <c r="C39">
         <v>1.39</v>
@@ -797,7 +797,7 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>1.194224267323106</v>
+        <v>1.177544138706092</v>
       </c>
       <c r="C40">
         <v>1.39</v>
@@ -808,7 +808,7 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>1.245996804749773</v>
+        <v>1.212129419096382</v>
       </c>
       <c r="C41">
         <v>1.39</v>
@@ -819,7 +819,7 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>1.14810497119427</v>
+        <v>1.089539121823629</v>
       </c>
       <c r="C42">
         <v>1.39</v>
@@ -830,7 +830,7 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>1.140981460300467</v>
+        <v>1.075159895976973</v>
       </c>
       <c r="C43">
         <v>1.39</v>
@@ -841,7 +841,7 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>1.21051084531026</v>
+        <v>1.119917346259883</v>
       </c>
       <c r="C44">
         <v>1.39</v>
@@ -852,7 +852,7 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>1.112558040561237</v>
+        <v>1.018747938559846</v>
       </c>
       <c r="C45">
         <v>1.39</v>
@@ -863,7 +863,7 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>1.136029477097558</v>
+        <v>1.048200281457596</v>
       </c>
       <c r="C46">
         <v>1.39</v>
@@ -874,7 +874,7 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>1.224187673966418</v>
+        <v>1.122040768543648</v>
       </c>
       <c r="C47">
         <v>1.39</v>
@@ -885,7 +885,7 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>1.201407276633915</v>
+        <v>1.106714923109522</v>
       </c>
       <c r="C48">
         <v>1.39</v>
@@ -896,7 +896,7 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>1.233008874355831</v>
+        <v>1.12843143705363</v>
       </c>
       <c r="C49">
         <v>1.39</v>
@@ -907,7 +907,7 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>1.223672701358401</v>
+        <v>1.117808792658574</v>
       </c>
       <c r="C50">
         <v>1.39</v>
@@ -961,10 +961,10 @@
         <v>175552.4789046343</v>
       </c>
       <c r="D2">
-        <v>3035998.758195594</v>
+        <v>4892088.187624219</v>
       </c>
       <c r="E2">
-        <v>317901.0430100303</v>
+        <v>496708.0866454329</v>
       </c>
     </row>
     <row r="3">
@@ -978,10 +978,10 @@
         <v>168195.3800873102</v>
       </c>
       <c r="D3">
-        <v>3948628.621034544</v>
+        <v>6435745.204400763</v>
       </c>
       <c r="E3">
-        <v>323952.9385300164</v>
+        <v>511417.1820336476</v>
       </c>
     </row>
     <row r="4">
@@ -995,10 +995,10 @@
         <v>181375.8754561994</v>
       </c>
       <c r="D4">
-        <v>5712564.944646887</v>
+        <v>9312255.93171319</v>
       </c>
       <c r="E4">
-        <v>359944.772316128</v>
+        <v>574232.1729739717</v>
       </c>
     </row>
     <row r="5">
@@ -1012,10 +1012,10 @@
         <v>250932.3110860498</v>
       </c>
       <c r="D5">
-        <v>6964350.14672369</v>
+        <v>11321667.59898222</v>
       </c>
       <c r="E5">
-        <v>501266.6502584897</v>
+        <v>800387.9182267141</v>
       </c>
     </row>
     <row r="6">
@@ -1029,10 +1029,10 @@
         <v>277769.8568456457</v>
       </c>
       <c r="D6">
-        <v>8127175.367859315</v>
+        <v>13107042.08411535</v>
       </c>
       <c r="E6">
-        <v>553990.4062026171</v>
+        <v>881128.8254041082</v>
       </c>
     </row>
     <row r="7">
@@ -1046,10 +1046,10 @@
         <v>450131.3112412578</v>
       </c>
       <c r="D7">
-        <v>8133239.159525326</v>
+        <v>12939519.9237324</v>
       </c>
       <c r="E7">
-        <v>887762.6549874599</v>
+        <v>1398659.303901674</v>
       </c>
     </row>
     <row r="8">
@@ -1063,10 +1063,10 @@
         <v>631415.5071628207</v>
       </c>
       <c r="D8">
-        <v>7687669.57414314</v>
+        <v>12135514.48596472</v>
       </c>
       <c r="E8">
-        <v>1239970.384653626</v>
+        <v>1939142.807164122</v>
       </c>
     </row>
     <row r="9">
@@ -1080,10 +1080,10 @@
         <v>714022.3781466705</v>
       </c>
       <c r="D9">
-        <v>7057303.141152964</v>
+        <v>11130966.90618035</v>
       </c>
       <c r="E9">
-        <v>1418199.70717808</v>
+        <v>2211530.247921448</v>
       </c>
     </row>
     <row r="10">
@@ -1097,10 +1097,10 @@
         <v>675734.4875321677</v>
       </c>
       <c r="D10">
-        <v>6721764.824851676</v>
+        <v>10619829.90352301</v>
       </c>
       <c r="E10">
-        <v>1373269.3480529</v>
+        <v>2156816.183576124</v>
       </c>
     </row>
     <row r="11">
@@ -1114,10 +1114,10 @@
         <v>638196.4686547145</v>
       </c>
       <c r="D11">
-        <v>6125295.629452349</v>
+        <v>9793464.228160882</v>
       </c>
       <c r="E11">
-        <v>1321563.976985453</v>
+        <v>2091429.180347891</v>
       </c>
     </row>
     <row r="12">
@@ -1131,10 +1131,10 @@
         <v>607017.8308207151</v>
       </c>
       <c r="D12">
-        <v>5724252.912354455</v>
+        <v>9125851.380475048</v>
       </c>
       <c r="E12">
-        <v>1214251.479870412</v>
+        <v>1910069.129355349</v>
       </c>
     </row>
     <row r="13">
@@ -1148,10 +1148,10 @@
         <v>604558.073261812</v>
       </c>
       <c r="D13">
-        <v>5361047.49007086</v>
+        <v>8447141.608589415</v>
       </c>
       <c r="E13">
-        <v>1161451.184250085</v>
+        <v>1813877.944278347</v>
       </c>
     </row>
     <row r="14">
@@ -1165,10 +1165,10 @@
         <v>611109.9278409031</v>
       </c>
       <c r="D14">
-        <v>5276086.102888305</v>
+        <v>8230306.391051994</v>
       </c>
       <c r="E14">
-        <v>1130865.814030638</v>
+        <v>1751783.561271023</v>
       </c>
     </row>
     <row r="15">
@@ -1182,10 +1182,10 @@
         <v>621617.2893283615</v>
       </c>
       <c r="D15">
-        <v>5269192.711253908</v>
+        <v>8174615.768605549</v>
       </c>
       <c r="E15">
-        <v>1119989.099063435</v>
+        <v>1724512.786140679</v>
       </c>
     </row>
     <row r="16">
@@ -1199,10 +1199,10 @@
         <v>611017.939574784</v>
       </c>
       <c r="D16">
-        <v>5093466.182145818</v>
+        <v>7901326.284292201</v>
       </c>
       <c r="E16">
-        <v>1073376.073668437</v>
+        <v>1649045.560022179</v>
       </c>
     </row>
     <row r="17">
@@ -1216,10 +1216,10 @@
         <v>548366.4853202614</v>
       </c>
       <c r="D17">
-        <v>4711349.627146987</v>
+        <v>7266103.90697923</v>
       </c>
       <c r="E17">
-        <v>953387.4035745296</v>
+        <v>1468657.227758406</v>
       </c>
     </row>
     <row r="18">
@@ -1233,10 +1233,10 @@
         <v>571977.945633658</v>
       </c>
       <c r="D18">
-        <v>4191817.26045708</v>
+        <v>6440375.83126989</v>
       </c>
       <c r="E18">
-        <v>987980.2596018547</v>
+        <v>1524742.038515197</v>
       </c>
     </row>
     <row r="19">
@@ -1250,10 +1250,10 @@
         <v>644284.7691245348</v>
       </c>
       <c r="D19">
-        <v>3436325.033557948</v>
+        <v>5277710.999557521</v>
       </c>
       <c r="E19">
-        <v>1108384.497388091</v>
+        <v>1710912.747431739</v>
       </c>
     </row>
     <row r="20">
@@ -1267,10 +1267,10 @@
         <v>520858.4286069481</v>
       </c>
       <c r="D20">
-        <v>3103521.514746078</v>
+        <v>4728502.680174099</v>
       </c>
       <c r="E20">
-        <v>881192.2401597816</v>
+        <v>1360710.954003355</v>
       </c>
     </row>
     <row r="21">
@@ -1284,10 +1284,10 @@
         <v>465649.8328263983</v>
       </c>
       <c r="D21">
-        <v>2525513.603155257</v>
+        <v>3888582.257771853</v>
       </c>
       <c r="E21">
-        <v>768887.7652658421</v>
+        <v>1182876.950025827</v>
       </c>
     </row>
     <row r="22">
@@ -1301,10 +1301,10 @@
         <v>404371.9984340814</v>
       </c>
       <c r="D22">
-        <v>2225807.20213801</v>
+        <v>3487797.726468408</v>
       </c>
       <c r="E22">
-        <v>650003.24022779</v>
+        <v>999152.3216797628</v>
       </c>
     </row>
     <row r="23">
@@ -1318,10 +1318,10 @@
         <v>311712.9536121772</v>
       </c>
       <c r="D23">
-        <v>2031145.156750803</v>
+        <v>3237567.692425488</v>
       </c>
       <c r="E23">
-        <v>497309.5890080909</v>
+        <v>776357.4785792965</v>
       </c>
     </row>
     <row r="24">
@@ -1335,10 +1335,10 @@
         <v>286903.6384188071</v>
       </c>
       <c r="D24">
-        <v>1624467.079142717</v>
+        <v>2629949.972404535</v>
       </c>
       <c r="E24">
-        <v>463574.8023292369</v>
+        <v>737439.123488741</v>
       </c>
     </row>
     <row r="25">
@@ -1352,10 +1352,10 @@
         <v>269748.3637777008</v>
       </c>
       <c r="D25">
-        <v>1784593.603857828</v>
+        <v>2903777.11231305</v>
       </c>
       <c r="E25">
-        <v>441841.5971651183</v>
+        <v>709957.1609873226</v>
       </c>
     </row>
     <row r="26">
@@ -1369,10 +1369,10 @@
         <v>253572.2008965711</v>
       </c>
       <c r="D26">
-        <v>2081924.541612861</v>
+        <v>3408186.233004656</v>
       </c>
       <c r="E26">
-        <v>417179.3555880819</v>
+        <v>672666.8721316673</v>
       </c>
     </row>
     <row r="27">
@@ -1386,10 +1386,10 @@
         <v>218222.4811873815</v>
       </c>
       <c r="D27">
-        <v>2200426.991267793</v>
+        <v>3669011.152556674</v>
       </c>
       <c r="E27">
-        <v>359820.2987067073</v>
+        <v>582707.4719599612</v>
       </c>
     </row>
     <row r="28">
@@ -1403,10 +1403,10 @@
         <v>209432.4955930643</v>
       </c>
       <c r="D28">
-        <v>2362109.322532767</v>
+        <v>3870097.521376645</v>
       </c>
       <c r="E28">
-        <v>347059.3167761965</v>
+        <v>560896.7923868399</v>
       </c>
     </row>
     <row r="29">
@@ -1420,10 +1420,10 @@
         <v>240489.5585583791</v>
       </c>
       <c r="D29">
-        <v>2052689.507634928</v>
+        <v>3293798.397944062</v>
       </c>
       <c r="E29">
-        <v>402479.2900108373</v>
+        <v>644609.9165422289</v>
       </c>
     </row>
     <row r="30">
@@ -1437,10 +1437,10 @@
         <v>297426.307245929</v>
       </c>
       <c r="D30">
-        <v>1874375.705839005</v>
+        <v>2937019.293739696</v>
       </c>
       <c r="E30">
-        <v>498039.7198405658</v>
+        <v>791528.1648264057</v>
       </c>
     </row>
     <row r="31">
@@ -1454,10 +1454,10 @@
         <v>330932.4600114336</v>
       </c>
       <c r="D31">
-        <v>2057099.26109698</v>
+        <v>3175071.763549678</v>
       </c>
       <c r="E31">
-        <v>559060.5112489692</v>
+        <v>882351.3904897656</v>
       </c>
     </row>
     <row r="32">
@@ -1471,10 +1471,10 @@
         <v>304494.0099764777</v>
       </c>
       <c r="D32">
-        <v>2162546.589682247</v>
+        <v>3435876.861879996</v>
       </c>
       <c r="E32">
-        <v>508461.4339099066</v>
+        <v>801840.0815664725</v>
       </c>
     </row>
     <row r="33">
@@ -1488,10 +1488,10 @@
         <v>312887.6336955865</v>
       </c>
       <c r="D33">
-        <v>2700725.754267067</v>
+        <v>4422731.091049726</v>
       </c>
       <c r="E33">
-        <v>511175.37399387</v>
+        <v>807430.592764706</v>
       </c>
     </row>
     <row r="34">
@@ -1505,10 +1505,10 @@
         <v>314534.6723136795</v>
       </c>
       <c r="D34">
-        <v>3365577.569938309</v>
+        <v>5610770.608904399</v>
       </c>
       <c r="E34">
-        <v>501272.8222174208</v>
+        <v>797355.0383768076</v>
       </c>
     </row>
     <row r="35">
@@ -1522,10 +1522,10 @@
         <v>424060.5247950304</v>
       </c>
       <c r="D35">
-        <v>3335140.270757179</v>
+        <v>5575461.938055868</v>
       </c>
       <c r="E35">
-        <v>671927.0884498185</v>
+        <v>1076969.944267382</v>
       </c>
     </row>
     <row r="36">
@@ -1539,10 +1539,10 @@
         <v>485520.9946334239</v>
       </c>
       <c r="D36">
-        <v>3275058.8898282</v>
+        <v>5308076.814128302</v>
       </c>
       <c r="E36">
-        <v>772001.0316701664</v>
+        <v>1223386.851181539</v>
       </c>
     </row>
     <row r="37">
@@ -1556,10 +1556,10 @@
         <v>511292.9463580013</v>
       </c>
       <c r="D37">
-        <v>3246293.757988465</v>
+        <v>5197617.959144453</v>
       </c>
       <c r="E37">
-        <v>812302.0764937559</v>
+        <v>1270507.64858262</v>
       </c>
     </row>
     <row r="38">
@@ -1573,10 +1573,10 @@
         <v>557740.1601458053</v>
       </c>
       <c r="D38">
-        <v>3903787.844199528</v>
+        <v>6292668.747533388</v>
       </c>
       <c r="E38">
-        <v>879197.6613986334</v>
+        <v>1364799.464487035</v>
       </c>
     </row>
     <row r="39">
@@ -1590,10 +1590,10 @@
         <v>438323.6301207932</v>
       </c>
       <c r="D39">
-        <v>5922134.757692982</v>
+        <v>9804502.183574447</v>
       </c>
       <c r="E39">
-        <v>684870.1160556627</v>
+        <v>1063601.781044925</v>
       </c>
     </row>
     <row r="40">
@@ -1607,10 +1607,10 @@
         <v>420927.8490202263</v>
       </c>
       <c r="D40">
-        <v>5616752.661185066</v>
+        <v>9274853.744130814</v>
       </c>
       <c r="E40">
-        <v>661337.0666063643</v>
+        <v>1044637.669641868</v>
       </c>
     </row>
     <row r="41">
@@ -1624,10 +1624,10 @@
         <v>448328.896348957</v>
       </c>
       <c r="D41">
-        <v>5421793.375482589</v>
+        <v>8718403.86379583</v>
       </c>
       <c r="E41">
-        <v>713202.0132133355</v>
+        <v>1135875.163748278</v>
       </c>
     </row>
     <row r="42">
@@ -1641,10 +1641,10 @@
         <v>613708.4574122744</v>
       </c>
       <c r="D42">
-        <v>3998052.999812827</v>
+        <v>6259377.850337231</v>
       </c>
       <c r="E42">
-        <v>989996.2226312272</v>
+        <v>1548517.114046755</v>
       </c>
     </row>
     <row r="43">
@@ -1658,10 +1658,10 @@
         <v>610380.9893202846</v>
       </c>
       <c r="D43">
-        <v>3522472.907053827</v>
+        <v>5414309.998288164</v>
       </c>
       <c r="E43">
-        <v>998469.8651368673</v>
+        <v>1541893.057030902</v>
       </c>
     </row>
     <row r="44">
@@ -1675,10 +1675,10 @@
         <v>505132.5923564186</v>
       </c>
       <c r="D44">
-        <v>3244191.001352493</v>
+        <v>4957472.382662123</v>
       </c>
       <c r="E44">
-        <v>826955.76546854</v>
+        <v>1267242.628882774</v>
       </c>
     </row>
     <row r="45">
@@ -1692,10 +1692,10 @@
         <v>385122.2940255876</v>
       </c>
       <c r="D45">
-        <v>2928703.536607862</v>
+        <v>4520974.802295398</v>
       </c>
       <c r="E45">
-        <v>627709.2616921717</v>
+        <v>960684.8405010251</v>
       </c>
     </row>
     <row r="46">
@@ -1709,10 +1709,10 @@
         <v>412444.8570698298</v>
       </c>
       <c r="D46">
-        <v>3462252.010470998</v>
+        <v>5360930.415973336</v>
       </c>
       <c r="E46">
-        <v>661612.4395295742</v>
+        <v>1018788.293366545</v>
       </c>
     </row>
     <row r="47">
@@ -1726,10 +1726,10 @@
         <v>407158.2879914262</v>
       </c>
       <c r="D47">
-        <v>3371184.275593183</v>
+        <v>5287756.384149029</v>
       </c>
       <c r="E47">
-        <v>649690.141245365</v>
+        <v>1005097.512445034</v>
       </c>
     </row>
     <row r="48">
@@ -1743,10 +1743,10 @@
         <v>435992.6220992496</v>
       </c>
       <c r="D48">
-        <v>3033901.468778184</v>
+        <v>4800870.302652473</v>
       </c>
       <c r="E48">
-        <v>708142.3733444787</v>
+        <v>1103379.916056668</v>
       </c>
     </row>
     <row r="49">
@@ -1760,10 +1760,10 @@
         <v>429762.341935744</v>
       </c>
       <c r="D49">
-        <v>2784235.173256356</v>
+        <v>4422474.906669284</v>
       </c>
       <c r="E49">
-        <v>720234.452307819</v>
+        <v>1131987.433941363</v>
       </c>
     </row>
     <row r="50">
@@ -1777,10 +1777,10 @@
         <v>415905.7003800459</v>
       </c>
       <c r="D50">
-        <v>2479322.611261403</v>
+        <v>3960818.44812993</v>
       </c>
       <c r="E50">
-        <v>720071.3808975153</v>
+        <v>1136094.09473712</v>
       </c>
     </row>
   </sheetData>
@@ -1810,7 +1810,7 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>565808.3437864749</v>
+        <v>989332.9055082767</v>
       </c>
     </row>
     <row r="3">
@@ -1818,7 +1818,7 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>672834.7065894996</v>
+        <v>1182133.484147389</v>
       </c>
     </row>
     <row r="4">
@@ -1826,7 +1826,7 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>981475.8915260585</v>
+        <v>1707665.019942419</v>
       </c>
     </row>
     <row r="5">
@@ -1834,7 +1834,7 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>804541.537650367</v>
+        <v>1476879.109678269</v>
       </c>
     </row>
     <row r="6">
@@ -1842,7 +1842,7 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>656400.2604832116</v>
+        <v>1334464.008717323</v>
       </c>
     </row>
     <row r="7">
@@ -1850,7 +1850,7 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>463112.094482751</v>
+        <v>979663.6450386979</v>
       </c>
     </row>
     <row r="8">
@@ -1858,7 +1858,7 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>468609.0265636053</v>
+        <v>975811.0757107341</v>
       </c>
     </row>
     <row r="9">
@@ -1866,7 +1866,7 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>464227.4937972752</v>
+        <v>906393.3082379188</v>
       </c>
     </row>
     <row r="10">
@@ -1874,7 +1874,7 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>601180.1297192568</v>
+        <v>1045477.200677469</v>
       </c>
     </row>
     <row r="11">
@@ -1882,7 +1882,7 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>463873.7477250121</v>
+        <v>818123.2048008707</v>
       </c>
     </row>
     <row r="12">
@@ -1890,7 +1890,7 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>321608.0375919272</v>
+        <v>632463.4020718432</v>
       </c>
     </row>
     <row r="13">
@@ -1898,7 +1898,7 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>320208.6041310969</v>
+        <v>610183.7483864705</v>
       </c>
     </row>
     <row r="14">
@@ -1906,7 +1906,7 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>493795.9546564154</v>
+        <v>833608.8692841213</v>
       </c>
     </row>
     <row r="15">
@@ -1914,7 +1914,7 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>582337.6236889205</v>
+        <v>919743.2684070499</v>
       </c>
     </row>
     <row r="16">
@@ -1922,7 +1922,7 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>421342.1922548235</v>
+        <v>684933.8358301652</v>
       </c>
     </row>
     <row r="17">
@@ -1930,7 +1930,7 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>358752.8034420264</v>
+        <v>577415.5561704341</v>
       </c>
     </row>
     <row r="18">
@@ -1938,7 +1938,7 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>276619.8409220167</v>
+        <v>442222.8936376525</v>
       </c>
     </row>
     <row r="19">
@@ -1946,7 +1946,7 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>209854.4399241378</v>
+        <v>337692.7913487221</v>
       </c>
     </row>
     <row r="20">
@@ -1954,7 +1954,7 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>362165.3896218904</v>
+        <v>522828.9976108707</v>
       </c>
     </row>
     <row r="21">
@@ -1962,7 +1962,7 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>258936.0620098945</v>
+        <v>397422.3803792119</v>
       </c>
     </row>
     <row r="22">
@@ -1970,7 +1970,7 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>205920.502978744</v>
+        <v>341371.773762054</v>
       </c>
     </row>
     <row r="23">
@@ -1978,7 +1978,7 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>168528.4582069018</v>
+        <v>337595.1295741249</v>
       </c>
     </row>
     <row r="24">
@@ -1986,7 +1986,7 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>126883.7434867801</v>
+        <v>266742.0335885538</v>
       </c>
     </row>
     <row r="25">
@@ -1994,7 +1994,7 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>274441.782631506</v>
+        <v>473398.6520334455</v>
       </c>
     </row>
     <row r="26">
@@ -2002,7 +2002,7 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>395493.909905154</v>
+        <v>668259.3795420906</v>
       </c>
     </row>
     <row r="27">
@@ -2010,7 +2010,7 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>237735.3011597943</v>
+        <v>469127.4226670903</v>
       </c>
     </row>
     <row r="28">
@@ -2018,7 +2018,7 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>249666.1393856967</v>
+        <v>489148.5761936274</v>
       </c>
     </row>
     <row r="29">
@@ -2026,7 +2026,7 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>157503.963768131</v>
+        <v>319011.9563522795</v>
       </c>
     </row>
     <row r="30">
@@ -2034,7 +2034,7 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>209515.9392932192</v>
+        <v>347860.8318345822</v>
       </c>
     </row>
     <row r="31">
@@ -2042,7 +2042,7 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>397883.9241127404</v>
+        <v>559376.2372562786</v>
       </c>
     </row>
     <row r="32">
@@ -2050,7 +2050,7 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>400732.6398456627</v>
+        <v>590272.4608856749</v>
       </c>
     </row>
     <row r="33">
@@ -2058,7 +2058,7 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>465011.9323850896</v>
+        <v>761678.5924243224</v>
       </c>
     </row>
     <row r="34">
@@ -2066,7 +2066,7 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>420470.8632191192</v>
+        <v>758286.2004548098</v>
       </c>
     </row>
     <row r="35">
@@ -2074,7 +2074,7 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>275895.9447982733</v>
+        <v>700391.1943550598</v>
       </c>
     </row>
     <row r="36">
@@ -2082,7 +2082,7 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>276873.530501748</v>
+        <v>626055.6316291477</v>
       </c>
     </row>
     <row r="37">
@@ -2090,7 +2090,7 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>219955.226306591</v>
+        <v>499711.3835017253</v>
       </c>
     </row>
     <row r="38">
@@ -2098,7 +2098,7 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>618165.3955467022</v>
+        <v>1120684.114557043</v>
       </c>
     </row>
     <row r="39">
@@ -2106,7 +2106,7 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>722721.2111155097</v>
+        <v>1317823.133791722</v>
       </c>
     </row>
     <row r="40">
@@ -2114,7 +2114,7 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>329970.1285124361</v>
+        <v>861830.7182491312</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>148036.7358404725</v>
+        <v>595268.8137042705</v>
       </c>
     </row>
     <row r="42">
@@ -2130,7 +2130,7 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>102718.2813950759</v>
+        <v>369923.4319141548</v>
       </c>
     </row>
     <row r="43">
@@ -2138,7 +2138,7 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>261033.8115212174</v>
+        <v>499424.5388599552</v>
       </c>
     </row>
     <row r="44">
@@ -2146,7 +2146,7 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>394619.2037358399</v>
+        <v>627432.0411159365</v>
       </c>
     </row>
     <row r="45">
@@ -2154,7 +2154,7 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>230289.1749124965</v>
+        <v>378820.9356288022</v>
       </c>
     </row>
     <row r="46">
@@ -2162,7 +2162,7 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>376901.210193265</v>
+        <v>600818.1816873457</v>
       </c>
     </row>
     <row r="47">
@@ -2170,7 +2170,7 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>317330.1302623357</v>
+        <v>531330.9343621028</v>
       </c>
     </row>
     <row r="48">
@@ -2178,7 +2178,7 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>173574.1914551917</v>
+        <v>359211.8134512114</v>
       </c>
     </row>
     <row r="49">
@@ -2186,7 +2186,7 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>201289.4344942649</v>
+        <v>383770.9572880365</v>
       </c>
     </row>
     <row r="50">
@@ -2194,7 +2194,7 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>214543.6900729825</v>
+        <v>379198.850338781</v>
       </c>
     </row>
   </sheetData>
@@ -2229,10 +2229,10 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>818901.7438421543</v>
+        <v>1280794.747233632</v>
       </c>
       <c r="C2">
-        <v>3127090.790178705</v>
+        <v>5093502.08716672</v>
       </c>
     </row>
     <row r="3">
@@ -2240,10 +2240,10 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>692469.5923369258</v>
+        <v>1092864.141047293</v>
       </c>
       <c r="C3">
-        <v>4115167.563669467</v>
+        <v>6727926.518978002</v>
       </c>
     </row>
     <row r="4">
@@ -2251,10 +2251,10 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>1119171.52418877</v>
+        <v>1780863.467948885</v>
       </c>
       <c r="C4">
-        <v>6313406.095968594</v>
+        <v>10296486.63840728</v>
       </c>
     </row>
     <row r="5">
@@ -2262,10 +2262,10 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>1719710.361526844</v>
+        <v>2735054.805896373</v>
       </c>
       <c r="C5">
-        <v>6920176.702611217</v>
+        <v>11219584.86774819</v>
       </c>
     </row>
     <row r="6">
@@ -2273,10 +2273,10 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>2523342.227527448</v>
+        <v>3990772.353531491</v>
       </c>
       <c r="C6">
-        <v>7348706.073728448</v>
+        <v>11783741.23608071</v>
       </c>
     </row>
     <row r="7">
@@ -2284,10 +2284,10 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>3523275.58687141</v>
+        <v>5532882.81187406</v>
       </c>
       <c r="C7">
-        <v>6033892.201803592</v>
+        <v>9583689.96752039</v>
       </c>
     </row>
     <row r="8">
@@ -2295,10 +2295,10 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>3807595.365578287</v>
+        <v>5943700.094014553</v>
       </c>
       <c r="C8">
-        <v>5965329.76453747</v>
+        <v>9429122.255438194</v>
       </c>
     </row>
     <row r="9">
@@ -2306,10 +2306,10 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>3125519.62077599</v>
+        <v>4878877.019811653</v>
       </c>
       <c r="C9">
-        <v>5236252.083315586</v>
+        <v>8300353.623439295</v>
       </c>
     </row>
     <row r="10">
@@ -2317,10 +2317,10 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>2703045.908708634</v>
+        <v>4261746.898227393</v>
       </c>
       <c r="C10">
-        <v>5444132.054492569</v>
+        <v>8647683.115636894</v>
       </c>
     </row>
     <row r="11">
@@ -2328,10 +2328,10 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>2420157.671398826</v>
+        <v>3825619.664042133</v>
       </c>
       <c r="C11">
-        <v>4866519.325737772</v>
+        <v>7773300.788927545</v>
       </c>
     </row>
     <row r="12">
@@ -2339,10 +2339,10 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>2343761.727040155</v>
+        <v>3681074.649674975</v>
       </c>
       <c r="C12">
-        <v>4347043.97707231</v>
+        <v>6909501.290492944</v>
       </c>
     </row>
     <row r="13">
@@ -2350,10 +2350,10 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>2779488.021823645</v>
+        <v>4340955.247694949</v>
       </c>
       <c r="C13">
-        <v>3831289.855242538</v>
+        <v>6022819.930404414</v>
       </c>
     </row>
     <row r="14">
@@ -2361,10 +2361,10 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>2288605.233025757</v>
+        <v>3537506.775067099</v>
       </c>
       <c r="C14">
-        <v>3955314.484059888</v>
+        <v>6184576.694321994</v>
       </c>
     </row>
     <row r="15">
@@ -2372,10 +2372,10 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>1844358.225399732</v>
+        <v>2837570.751692261</v>
       </c>
       <c r="C15">
-        <v>4064879.416593348</v>
+        <v>6320781.568416995</v>
       </c>
     </row>
     <row r="16">
@@ -2383,10 +2383,10 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>1733302.52894104</v>
+        <v>2669866.483848505</v>
       </c>
       <c r="C16">
-        <v>3679795.860359211</v>
+        <v>5704085.627960069</v>
       </c>
     </row>
     <row r="17">
@@ -2394,10 +2394,10 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>2133935.747796869</v>
+        <v>3297175.099689086</v>
       </c>
       <c r="C17">
-        <v>3318474.749323837</v>
+        <v>5093985.191910435</v>
       </c>
     </row>
     <row r="18">
@@ -2405,10 +2405,10 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>2065036.410727433</v>
+        <v>3186528.691400778</v>
       </c>
       <c r="C18">
-        <v>2670591.277151921</v>
+        <v>4090936.349166114</v>
       </c>
     </row>
     <row r="19">
@@ -2416,10 +2416,10 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>1674262.634586988</v>
+        <v>2583010.90845543</v>
       </c>
       <c r="C19">
-        <v>2114846.582141691</v>
+        <v>3240955.390428884</v>
       </c>
     </row>
     <row r="20">
@@ -2427,10 +2427,10 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>1274756.635587564</v>
+        <v>1964722.145742689</v>
       </c>
       <c r="C20">
-        <v>2203859.472115347</v>
+        <v>3339961.388999697</v>
       </c>
     </row>
     <row r="21">
@@ -2438,10 +2438,10 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>1039829.687945345</v>
+        <v>1598660.478185605</v>
       </c>
       <c r="C21">
-        <v>1858008.5005847</v>
+        <v>2877076.237865971</v>
       </c>
     </row>
     <row r="22">
@@ -2449,10 +2449,10 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>799774.8959190156</v>
+        <v>1232668.646828766</v>
       </c>
       <c r="C22">
-        <v>1592874.844645676</v>
+        <v>2529727.208404311</v>
       </c>
     </row>
     <row r="23">
@@ -2460,10 +2460,10 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>1009378.136155477</v>
+        <v>1592960.473504868</v>
       </c>
       <c r="C23">
-        <v>1508997.841062149</v>
+        <v>2433313.372250946</v>
       </c>
     </row>
     <row r="24">
@@ -2471,10 +2471,10 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>762954.6210647761</v>
+        <v>1220681.046879334</v>
       </c>
       <c r="C24">
-        <v>1168351.372074684</v>
+        <v>1911434.788272182</v>
       </c>
     </row>
     <row r="25">
@@ -2482,10 +2482,10 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>648711.1399721873</v>
+        <v>1044378.965471335</v>
       </c>
       <c r="C25">
-        <v>1596554.621821222</v>
+        <v>2636392.4168342</v>
       </c>
     </row>
     <row r="26">
@@ -2493,10 +2493,10 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>603504.6997222889</v>
+        <v>975487.9853669129</v>
       </c>
       <c r="C26">
-        <v>2060207.728072652</v>
+        <v>3396795.234861476</v>
       </c>
     </row>
     <row r="27">
@@ -2504,10 +2504,10 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>526886.2697501911</v>
+        <v>853296.0849624436</v>
       </c>
       <c r="C27">
-        <v>1744642.587122003</v>
+        <v>2898891.08749378</v>
       </c>
     </row>
     <row r="28">
@@ -2515,10 +2515,10 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>897209.5005985997</v>
+        <v>1455473.250388013</v>
       </c>
       <c r="C28">
-        <v>1834103.316129021</v>
+        <v>2971395.303458828</v>
       </c>
     </row>
     <row r="29">
@@ -2526,10 +2526,10 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>1106699.562181479</v>
+        <v>1775146.73754667</v>
       </c>
       <c r="C29">
-        <v>1405439.472980234</v>
+        <v>2234919.978061272</v>
       </c>
     </row>
     <row r="30">
@@ -2537,10 +2537,10 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>897690.4217553301</v>
+        <v>1422687.03420335</v>
       </c>
       <c r="C30">
-        <v>1390989.341114613</v>
+        <v>2152555.690674528</v>
       </c>
     </row>
     <row r="31">
@@ -2548,10 +2548,10 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>727987.612628901</v>
+        <v>1151422.399369721</v>
       </c>
       <c r="C31">
-        <v>1791354.121213139</v>
+        <v>2760057.757197319</v>
       </c>
     </row>
     <row r="32">
@@ -2559,10 +2559,10 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>580299.254984961</v>
+        <v>917631.0335443</v>
       </c>
       <c r="C32">
-        <v>1838227.812102924</v>
+        <v>2955920.679092173</v>
       </c>
     </row>
     <row r="33">
@@ -2570,10 +2570,10 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>607063.5267140283</v>
+        <v>969725.5039986669</v>
       </c>
       <c r="C33">
-        <v>2265404.603502725</v>
+        <v>3737550.760035496</v>
       </c>
     </row>
     <row r="34">
@@ -2581,10 +2581,10 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>912804.5434278145</v>
+        <v>1485079.361710488</v>
       </c>
       <c r="C34">
-        <v>2289961.8864225</v>
+        <v>3841653.137787165</v>
       </c>
     </row>
     <row r="35">
@@ -2592,10 +2592,10 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>1227615.744003769</v>
+        <v>1983849.916590142</v>
       </c>
       <c r="C35">
-        <v>2341665.367560621</v>
+        <v>3887057.262120029</v>
       </c>
     </row>
     <row r="36">
@@ -2603,10 +2603,10 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>1356365.27134778</v>
+        <v>2157409.503466189</v>
       </c>
       <c r="C36">
-        <v>2261715.055438231</v>
+        <v>3654983.473081213</v>
       </c>
     </row>
     <row r="37">
@@ -2614,10 +2614,10 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>1231401.864778639</v>
+        <v>1932181.14363161</v>
       </c>
       <c r="C37">
-        <v>1900319.74102412</v>
+        <v>3050855.593589794</v>
       </c>
     </row>
     <row r="38">
@@ -2625,10 +2625,10 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>1032183.954144622</v>
+        <v>1604450.476430877</v>
       </c>
       <c r="C38">
-        <v>4228326.482296822</v>
+        <v>6984216.656248598</v>
       </c>
     </row>
     <row r="39">
@@ -2636,10 +2636,10 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>1097605.613342867</v>
+        <v>1723372.758319499</v>
       </c>
       <c r="C39">
-        <v>5453410.631073124</v>
+        <v>9096496.56689905</v>
       </c>
     </row>
     <row r="40">
@@ -2647,10 +2647,10 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>847589.7677249339</v>
+        <v>1339239.49408536</v>
       </c>
       <c r="C40">
-        <v>4939315.956229024</v>
+        <v>8082855.944759051</v>
       </c>
     </row>
     <row r="41">
@@ -2658,10 +2658,10 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>3882443.287277925</v>
+        <v>6164858.23694787</v>
       </c>
       <c r="C41">
-        <v>4055224.918263834</v>
+        <v>6443800.108599192</v>
       </c>
     </row>
     <row r="42">
@@ -2669,10 +2669,10 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>2585274.507624729</v>
+        <v>4019162.912175963</v>
       </c>
       <c r="C42">
-        <v>2789701.559388924</v>
+        <v>4339956.406650594</v>
       </c>
     </row>
     <row r="43">
@@ -2680,10 +2680,10 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>1923496.553382277</v>
+        <v>2957054.247002357</v>
       </c>
       <c r="C43">
-        <v>2858836.407181586</v>
+        <v>4379553.338601422</v>
       </c>
     </row>
     <row r="44">
@@ -2691,10 +2691,10 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>1430605.629595596</v>
+        <v>2188916.661849292</v>
       </c>
       <c r="C44">
-        <v>3071852.705597342</v>
+        <v>4703024.405958902</v>
       </c>
     </row>
     <row r="45">
@@ -2702,10 +2702,10 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>984529.0974939265</v>
+        <v>1509280.097035531</v>
       </c>
       <c r="C45">
-        <v>2300517.232638885</v>
+        <v>3566073.339394645</v>
       </c>
     </row>
     <row r="46">
@@ -2713,10 +2713,10 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>1191683.384640264</v>
+        <v>1832800.354882278</v>
       </c>
       <c r="C46">
-        <v>2867447.37577673</v>
+        <v>4447520.250200345</v>
       </c>
     </row>
     <row r="47">
@@ -2724,10 +2724,10 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>1394047.569830063</v>
+        <v>2167184.345184588</v>
       </c>
       <c r="C47">
-        <v>2637714.949601834</v>
+        <v>4166511.568639169</v>
       </c>
     </row>
     <row r="48">
@@ -2735,10 +2735,10 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>1078224.688352826</v>
+        <v>1683214.89719497</v>
       </c>
       <c r="C48">
-        <v>2152741.595077149</v>
+        <v>3417721.44301607</v>
       </c>
     </row>
     <row r="49">
@@ -2746,10 +2746,10 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>1425391.509265588</v>
+        <v>2250909.782277399</v>
       </c>
       <c r="C49">
-        <v>2005656.068728045</v>
+        <v>3197732.869215666</v>
       </c>
     </row>
     <row r="50">
@@ -2757,10 +2757,10 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>1042048.510193462</v>
+        <v>1650081.108469494</v>
       </c>
       <c r="C50">
-        <v>1803534.525319292</v>
+        <v>2915668.137980746</v>
       </c>
     </row>
   </sheetData>
